--- a/artfynd/A 34521-2025 artfynd.xlsx
+++ b/artfynd/A 34521-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75631918</v>
+        <v>96661588</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östa 4,5 km NV om Lohärad kyrka, Upl</t>
+          <t>Östa SO, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698260.6350405749</v>
+        <v>698351</v>
       </c>
       <c r="R2" t="n">
-        <v>6638130.30177532</v>
+        <v>6637897</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1997-09-03</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1997-09-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>8 ex. på levande asp, omkr. 151 cm.</t>
+          <t>2021-10-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,43 +758,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Asp</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Levande asp. # Asp</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gillis Aronsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96661588</v>
+        <v>96661662</v>
       </c>
       <c r="B3" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,27 +792,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -855,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>698351.8496175093</v>
+        <v>698343</v>
       </c>
       <c r="R3" t="n">
-        <v>6637896.424161444</v>
+        <v>6638112</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,19 +860,9 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -932,41 +894,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96661653</v>
+        <v>96661611</v>
       </c>
       <c r="B4" t="n">
-        <v>85241</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91375</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3674</v>
+        <v>720</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -975,10 +940,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>698350.7822495512</v>
+        <v>698389</v>
       </c>
       <c r="R4" t="n">
-        <v>6638048.486576575</v>
+        <v>6637942</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,19 +973,9 @@
           <t>2021-10-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,61 +1007,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96661662</v>
+        <v>75631918</v>
       </c>
       <c r="B5" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>366</v>
+        <v>1205</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Östa SO, Upl</t>
+          <t>Östa 4,5 km NV om Lohärad kyrka, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>698342.8164666446</v>
+        <v>698261</v>
       </c>
       <c r="R5" t="n">
-        <v>6638112.533231884</v>
+        <v>6638130</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1133,22 +1081,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-09-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-10-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1997-09-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>8 ex. på levande asp, omkr. 151 cm.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,22 +1100,1445 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Levande asp. # Asp</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>96661631</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91436</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1357</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläckfingersvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramaria sanguinea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pers.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Östa SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>698416</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6637945</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Ossian Rydebjörk</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr">
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128110484</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97678</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2326</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vanlig rörsvepemossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Liochlaena lanceolata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Nees</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Erken, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>698459</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6637998</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96661653</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87309</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Östa SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>698351</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6638049</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>96661623</v>
+      </c>
+      <c r="B9" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Östa SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>698389</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6637942</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>96661572</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Östa SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>698398</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6637855</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>96661639</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Östa SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>698300</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6637946</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96661585</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91435</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Östa SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>698396</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6637910</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128110502</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Erken , Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>698449</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6637946</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128110375</v>
+      </c>
+      <c r="B14" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Erken, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>698464</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6638017</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128110386</v>
+      </c>
+      <c r="B15" t="n">
+        <v>75428</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Erken, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>698464</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6638018</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128106158</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Erken, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>698449</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6637992</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128110467</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Erken, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>698449</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6637992</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>96661633</v>
+      </c>
+      <c r="B18" t="n">
+        <v>91428</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Östa SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>698416</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6637945</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lohärad</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-10-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ossian Rydebjörk, Birgitta Wasstorp, Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
         </is>

--- a/artfynd/A 34521-2025 artfynd.xlsx
+++ b/artfynd/A 34521-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75631918</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96661588</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96661662</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
       <c r="AY5" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96661611</t>
         </is>
       </c>
     </row>
@@ -1228,6 +1253,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96661631</t>
         </is>
       </c>
     </row>
@@ -1342,6 +1372,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128110484</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96661653</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1552,6 +1592,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96661623</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1657,6 +1702,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96661572</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96661639</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1867,6 +1922,11 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96661585</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1978,6 +2038,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128110502</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2097,6 +2162,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128110375</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2208,6 +2278,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128110386</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2327,6 +2402,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128106158</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2438,6 +2518,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128110467</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2543,8 +2628,32 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96661633</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>